--- a/consent_forms/028_insurance_claim_investigation_consent_form--consent_forms.xlsx
+++ b/consent_forms/028_insurance_claim_investigation_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>Form Ids 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>insurer_name</t>
+          <t>insurer_name_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>insurer_name</t>
+          <t>Insurer Name 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
